--- a/DS-D files/Key messages.xlsx
+++ b/DS-D files/Key messages.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10503"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5FA83F01FFB69574/R/DDI/DS-D files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mitra/Documents/1 DDI/DDI earlier years/DDI Year 5 2025/DS-E 2025 files for review/filestocheck May 15th 2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="8_{115FF2DC-93EB-4FBD-B2A8-C0CC45B7190F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFB4E9F2-0B8E-4C46-A004-2151F482026A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91ED2AE5-FACE-ED40-9C96-15A8632C58E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{DF5D2554-F1D8-4083-8A6A-01334C00ED3B}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16380" xr2:uid="{DF5D2554-F1D8-4083-8A6A-01334C00ED3B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,13 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="113">
-  <si>
-    <t xml:space="preserve">The proportion of adults with disabilities varies across countries, with the lowest at 5%, the highest at 33%, and the median at 14.2%. </t>
-  </si>
-  <si>
-    <t>The proportion of households who have at least one adult with disabilities varies across countries with the lowest at 10.4%, the highest at 61.7%, and the median at 28.5%.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="173">
   <si>
     <t>Ever attended school</t>
   </si>
@@ -83,13 +77,7 @@
     <t>Family planning</t>
   </si>
   <si>
-    <t>Across countries, the proportion of women who report that they have their family planning needs met. In other words, women who want and have access to modern contraceptive methods, is similar, lower or higher for women with disabilities, compared to women without disabilities. There is no consistent pattern in the countries under study.</t>
-  </si>
-  <si>
     <t>Violence</t>
-  </si>
-  <si>
-    <t>In most of the countries under study, the proportion of women who report being subject to domestic violence by their intimate partner in the past 12 months is higher among women with disabilities, than among women without disabilities.</t>
   </si>
   <si>
     <t>Computer</t>
@@ -464,12 +452,6 @@
   </si>
   <si>
     <t>Proportion of adults ages 15 and older who live in households that have safely managed sanitation services.</t>
-  </si>
-  <si>
-    <t>Proportion of women who report that they have their family planning needs met; they want and have access to modern contraceptive methods.</t>
-  </si>
-  <si>
-    <t>Proportion of women who report being subject to domestic violence by their intimate partner in the past 12 months. Domestic violence may be physical, psychological or sexual.</t>
   </si>
   <si>
     <t xml:space="preserve">Proportion of adults ages 15 and older who have or use a computer.  </t>
@@ -616,12 +598,210 @@
   <si>
     <t>Insecurity</t>
   </si>
+  <si>
+    <t>BMI</t>
+  </si>
+  <si>
+    <t>Living alone</t>
+  </si>
+  <si>
+    <t>Obese</t>
+  </si>
+  <si>
+    <t>Raw</t>
+  </si>
+  <si>
+    <t>Multid poverty</t>
+  </si>
+  <si>
+    <t>Household death</t>
+  </si>
+  <si>
+    <t>Child died</t>
+  </si>
+  <si>
+    <t>Healthcare access</t>
+  </si>
+  <si>
+    <t>Clean</t>
+  </si>
+  <si>
+    <t>everattended_new</t>
+  </si>
+  <si>
+    <t>ind_atleastprimary</t>
+  </si>
+  <si>
+    <t>ind_atleastsecondary</t>
+  </si>
+  <si>
+    <t>lit_new</t>
+  </si>
+  <si>
+    <t>computer</t>
+  </si>
+  <si>
+    <t>internet</t>
+  </si>
+  <si>
+    <t>mobile_own</t>
+  </si>
+  <si>
+    <t>ind_emp</t>
+  </si>
+  <si>
+    <t>youth_idle</t>
+  </si>
+  <si>
+    <t>work_manufacturing</t>
+  </si>
+  <si>
+    <t>work_managerial</t>
+  </si>
+  <si>
+    <t>work_informal</t>
+  </si>
+  <si>
+    <t>ind_water</t>
+  </si>
+  <si>
+    <t>ind_toilet</t>
+  </si>
+  <si>
+    <t>fp_demsat_mod</t>
+  </si>
+  <si>
+    <t>anyviolence_byh_12m</t>
+  </si>
+  <si>
+    <t>bmi</t>
+  </si>
+  <si>
+    <t>overweight_obese</t>
+  </si>
+  <si>
+    <t>child_died</t>
+  </si>
+  <si>
+    <t>healthcare_prob</t>
+  </si>
+  <si>
+    <t>death_hh</t>
+  </si>
+  <si>
+    <t>alone</t>
+  </si>
+  <si>
+    <t>ind_electric</t>
+  </si>
+  <si>
+    <t>ind_cleanfuel</t>
+  </si>
+  <si>
+    <t>ind_livingcond</t>
+  </si>
+  <si>
+    <t>ind_asset_ownership</t>
+  </si>
+  <si>
+    <t>cell_new</t>
+  </si>
+  <si>
+    <t>health_insurance</t>
+  </si>
+  <si>
+    <t>social_prot</t>
+  </si>
+  <si>
+    <t>food_insecure</t>
+  </si>
+  <si>
+    <t>shock_any</t>
+  </si>
+  <si>
+    <t>health_exp_hh</t>
+  </si>
+  <si>
+    <t>ind_mdp</t>
+  </si>
+  <si>
+    <t>Overweight or obese</t>
+  </si>
+  <si>
+    <t>Problems accessing healthcare</t>
+  </si>
+  <si>
+    <t>Child mortality</t>
+  </si>
+  <si>
+    <t>Recent death in the household</t>
+  </si>
+  <si>
+    <t>Demographics</t>
+  </si>
+  <si>
+    <t>Adults who Live alone</t>
+  </si>
+  <si>
+    <t>The proportion of adults with disabilities varies across countries. The lowest is 5%. The highest is 37%. The median is 14.2%.</t>
+  </si>
+  <si>
+    <t>The proportion of households who have at least one adult with disabilities varies across countries. The lowest is 11.8%. The highest is 62.2%. The median at 31.8%.</t>
+  </si>
+  <si>
+    <t>The proportion of adults who live alone is higher among adults with disabilities than among adults without disabilities.</t>
+  </si>
+  <si>
+    <t>Across countries, the proportion of women who report that they have their family planning needs met is overall similar for women with disabilities compared to women without disabilities. There is no consistent disability gap in family planning needs met in the countries under study.</t>
+  </si>
+  <si>
+    <t>In most countries, women with disabilities have on average a higher BMI than women without disabilities.</t>
+  </si>
+  <si>
+    <t>In most countries, women with disabilities are more often overweight or obese than  women without disabilities.</t>
+  </si>
+  <si>
+    <t>In most countries, a higher proportion of women with disabilities report problems accessing health care compared to women without disabilities. Based on  a DDI study, multivariate analysis, after adjusting for social, demographic, and socioeconomic factors, shows a similar pattern, but results vary across countries (Mitra et al 2026)</t>
+  </si>
+  <si>
+    <t>The proportion of households who experienced a recent death is higher among households with disabilities than among households without disabilities.</t>
+  </si>
+  <si>
+    <t>In most countries, women with disabilities report domestic violence more often than women without disabilities. A DDI study shows that results vary across countries when social and economic factors are considered. But that overall, women with disabilities suffer a higher risk of domestic violence (Hervé, Theiss and Mitra 2025).</t>
+  </si>
+  <si>
+    <t>Proportion of adults ages 15 and older who live alone</t>
+  </si>
+  <si>
+    <t>Proportion of  households who experienced a recent death</t>
+  </si>
+  <si>
+    <t>Proportion of women ages 15 to 49 who report that they have their family planning needs met; they want and have access to modern contraceptive methods.</t>
+  </si>
+  <si>
+    <t>Proportion of womenages 15 to 49  who report being subject to domestic violence by their intimate partner in the past 12 months. Domestic violence may be physical, psychological or sexual.</t>
+  </si>
+  <si>
+    <t>BMI (Body Mass Index)  of women ages 15 to 49</t>
+  </si>
+  <si>
+    <t>Proportion of women ages 15 to 49 who are overweight or obese</t>
+  </si>
+  <si>
+    <t>Proportion of women ages 15 to 49 who report having problems accessing healthcare</t>
+  </si>
+  <si>
+    <t>Proportion of mothers ages 15 to 49  who experienced under five  child mortality</t>
+  </si>
+  <si>
+    <t>In most countries, mothers are more likely to experience the death of a child ages 5 or less, if the mother has a disability.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -666,13 +846,38 @@
       <name val="Aptos"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="8"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -687,8 +892,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1023,596 +1240,933 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F80B718-1375-4CF0-862D-AA7D94D95BA4}">
-  <dimension ref="A1:F30"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H36"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="37.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="33.85546875" customWidth="1"/>
+    <col min="1" max="1" width="37.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="23.5" customWidth="1"/>
+    <col min="6" max="6" width="49.5" customWidth="1"/>
+    <col min="7" max="7" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s">
         <v>104</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" t="s">
         <v>110</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G1" t="s">
+        <v>79</v>
+      </c>
+      <c r="H1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="G2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" t="s">
+        <v>83</v>
+      </c>
+      <c r="E3" t="s">
+        <v>83</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D4" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" t="s">
+        <v>137</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>0</v>
+      </c>
+      <c r="D5" t="s">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>116</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" t="s">
+        <v>54</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" t="s">
+        <v>117</v>
+      </c>
+      <c r="F6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" t="s">
+        <v>55</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>56</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>100</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s">
+        <v>86</v>
+      </c>
+      <c r="D8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" t="s">
+        <v>7</v>
+      </c>
+      <c r="G8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9" t="s">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s">
+        <v>58</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>101</v>
+      </c>
+      <c r="B10" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" t="s">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E10" t="s">
+        <v>129</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>101</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="H11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
+        <v>131</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" t="s">
+        <v>107</v>
+      </c>
+      <c r="D13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" t="s">
+        <v>132</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C14" t="s">
+        <v>109</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>133</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="H15" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" t="s">
+        <v>112</v>
+      </c>
+      <c r="D16" t="s">
+        <v>112</v>
+      </c>
+      <c r="E16" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C17" t="s">
+        <v>113</v>
+      </c>
+      <c r="D17" t="s">
+        <v>113</v>
+      </c>
+      <c r="E17" t="s">
+        <v>134</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
         <v>102</v>
       </c>
-      <c r="D1" t="s">
+      <c r="B18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" t="s">
+        <v>120</v>
+      </c>
+      <c r="F18" t="s">
+        <v>15</v>
+      </c>
+      <c r="G18" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>102</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>88</v>
+      </c>
+      <c r="D19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G19" t="s">
+        <v>66</v>
+      </c>
+      <c r="H19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" t="s">
+        <v>122</v>
+      </c>
+      <c r="F20" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>102</v>
+      </c>
+      <c r="B21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>20</v>
+      </c>
+      <c r="D21" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" t="s">
+        <v>123</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>102</v>
+      </c>
+      <c r="B22" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" t="s">
+        <v>89</v>
+      </c>
+      <c r="D22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" t="s">
+        <v>124</v>
+      </c>
+      <c r="F22" t="s">
+        <v>23</v>
+      </c>
+      <c r="G22" t="s">
+        <v>69</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>102</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
+        <v>24</v>
+      </c>
+      <c r="E23" t="s">
+        <v>125</v>
+      </c>
+      <c r="F23" t="s">
+        <v>25</v>
+      </c>
+      <c r="G23" t="s">
+        <v>61</v>
+      </c>
+      <c r="H23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>102</v>
+      </c>
+      <c r="B24" t="s">
+        <v>26</v>
+      </c>
+      <c r="C24" t="s">
+        <v>26</v>
+      </c>
+      <c r="D24" t="s">
+        <v>26</v>
+      </c>
+      <c r="E24" t="s">
+        <v>126</v>
+      </c>
+      <c r="F24" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>102</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" t="s">
+        <v>28</v>
+      </c>
+      <c r="E25" t="s">
+        <v>127</v>
+      </c>
+      <c r="F25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>103</v>
       </c>
-      <c r="E1" t="s">
-        <v>85</v>
-      </c>
-      <c r="F1" t="s">
+      <c r="B26" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" t="s">
+        <v>138</v>
+      </c>
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+      <c r="G26" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
+        <v>92</v>
+      </c>
+      <c r="D27" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" t="s">
+        <v>139</v>
+      </c>
+      <c r="F27" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" t="s">
+        <v>72</v>
+      </c>
+      <c r="H27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" t="s">
+        <v>34</v>
+      </c>
+      <c r="E28" t="s">
+        <v>140</v>
+      </c>
+      <c r="F28" t="s">
+        <v>35</v>
+      </c>
+      <c r="G28" t="s">
+        <v>73</v>
+      </c>
+      <c r="H28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>103</v>
+      </c>
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" t="s">
+        <v>93</v>
+      </c>
+      <c r="D29" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" t="s">
+        <v>141</v>
+      </c>
+      <c r="F29" t="s">
+        <v>37</v>
+      </c>
+      <c r="G29" t="s">
+        <v>63</v>
+      </c>
+      <c r="H29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>103</v>
+      </c>
+      <c r="B30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" t="s">
+        <v>94</v>
+      </c>
+      <c r="E30" t="s">
+        <v>142</v>
+      </c>
+      <c r="F30" t="s">
+        <v>39</v>
+      </c>
+      <c r="G30" t="s">
+        <v>74</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>106</v>
+      </c>
+      <c r="B31" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" t="s">
+        <v>143</v>
+      </c>
+      <c r="F31" t="s">
+        <v>41</v>
+      </c>
+      <c r="G31" t="s">
+        <v>75</v>
+      </c>
+      <c r="H31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" t="s">
+        <v>42</v>
+      </c>
+      <c r="C32" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" t="s">
+        <v>144</v>
+      </c>
+      <c r="F32" t="s">
+        <v>43</v>
+      </c>
+      <c r="G32" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" t="s">
+        <v>145</v>
+      </c>
+      <c r="F33" t="s">
+        <v>45</v>
+      </c>
+      <c r="G33" t="s">
+        <v>77</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s">
+        <v>95</v>
+      </c>
+      <c r="D34" t="s">
+        <v>95</v>
+      </c>
+      <c r="E34" t="s">
+        <v>146</v>
+      </c>
+      <c r="F34" t="s">
+        <v>47</v>
+      </c>
+      <c r="G34" t="s">
+        <v>78</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" t="s">
+        <v>48</v>
+      </c>
+      <c r="C35" t="s">
+        <v>48</v>
+      </c>
+      <c r="D35" t="s">
+        <v>48</v>
+      </c>
+      <c r="E35" t="s">
+        <v>147</v>
+      </c>
+      <c r="F35" t="s">
+        <v>49</v>
+      </c>
+      <c r="G35" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>50</v>
+      </c>
+      <c r="B36" t="s">
+        <v>50</v>
+      </c>
+      <c r="C36" t="s">
+        <v>50</v>
+      </c>
+      <c r="D36" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>105</v>
-      </c>
-      <c r="B2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C2" t="s">
-        <v>88</v>
-      </c>
-      <c r="D2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>58</v>
-      </c>
-      <c r="F4" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>106</v>
-      </c>
-      <c r="B5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>91</v>
-      </c>
-      <c r="D5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" t="s">
-        <v>59</v>
-      </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" t="s">
-        <v>60</v>
-      </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" t="s">
-        <v>92</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>62</v>
-      </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>107</v>
-      </c>
-      <c r="B9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" t="s">
-        <v>12</v>
-      </c>
-      <c r="D9" t="s">
-        <v>13</v>
-      </c>
-      <c r="E9" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>107</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
-      </c>
-      <c r="C10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>107</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" t="s">
+      <c r="E36" t="s">
+        <v>148</v>
+      </c>
+      <c r="F36" t="s">
+        <v>51</v>
+      </c>
+      <c r="G36" t="s">
         <v>65</v>
       </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>108</v>
-      </c>
-      <c r="B12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C12" t="s">
-        <v>93</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>108</v>
-      </c>
-      <c r="B13" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" t="s">
-        <v>21</v>
-      </c>
-      <c r="E13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>108</v>
-      </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" t="s">
-        <v>73</v>
-      </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>108</v>
-      </c>
-      <c r="B15" t="s">
-        <v>24</v>
-      </c>
-      <c r="C15" t="s">
-        <v>24</v>
-      </c>
-      <c r="D15" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" t="s">
-        <v>26</v>
-      </c>
-      <c r="C16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" t="s">
-        <v>27</v>
-      </c>
-      <c r="E16" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" t="s">
-        <v>28</v>
-      </c>
-      <c r="C17" t="s">
-        <v>28</v>
-      </c>
-      <c r="D17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" t="s">
-        <v>67</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>108</v>
-      </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" t="s">
-        <v>31</v>
-      </c>
-      <c r="E18" t="s">
-        <v>76</v>
-      </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>108</v>
-      </c>
-      <c r="B19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C19" t="s">
-        <v>32</v>
-      </c>
-      <c r="D19" t="s">
-        <v>33</v>
-      </c>
-      <c r="E19" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>109</v>
-      </c>
-      <c r="B20" t="s">
-        <v>34</v>
-      </c>
-      <c r="C20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" t="s">
-        <v>77</v>
-      </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>109</v>
-      </c>
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>98</v>
-      </c>
-      <c r="D21" t="s">
-        <v>37</v>
-      </c>
-      <c r="E21" t="s">
-        <v>78</v>
-      </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>109</v>
-      </c>
-      <c r="B22" t="s">
-        <v>38</v>
-      </c>
-      <c r="C22" t="s">
-        <v>38</v>
-      </c>
-      <c r="D22" t="s">
-        <v>39</v>
-      </c>
-      <c r="E22" t="s">
-        <v>79</v>
-      </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>109</v>
-      </c>
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" t="s">
-        <v>99</v>
-      </c>
-      <c r="D23" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" t="s">
-        <v>69</v>
-      </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>109</v>
-      </c>
-      <c r="B24" t="s">
-        <v>42</v>
-      </c>
-      <c r="C24" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" t="s">
-        <v>80</v>
-      </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" t="s">
-        <v>44</v>
-      </c>
-      <c r="C25" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" t="s">
-        <v>45</v>
-      </c>
-      <c r="E25" t="s">
-        <v>81</v>
-      </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>112</v>
-      </c>
-      <c r="B26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" t="s">
-        <v>47</v>
-      </c>
-      <c r="E26" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>112</v>
-      </c>
-      <c r="B27" t="s">
-        <v>48</v>
-      </c>
-      <c r="C27" t="s">
-        <v>48</v>
-      </c>
-      <c r="D27" t="s">
-        <v>49</v>
-      </c>
-      <c r="E27" t="s">
-        <v>83</v>
-      </c>
-      <c r="F27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>112</v>
-      </c>
-      <c r="B28" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" t="s">
-        <v>51</v>
-      </c>
-      <c r="E28" t="s">
-        <v>84</v>
-      </c>
-      <c r="F28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>112</v>
-      </c>
-      <c r="B29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" t="s">
-        <v>52</v>
-      </c>
-      <c r="D29" t="s">
-        <v>53</v>
-      </c>
-      <c r="E29" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" t="s">
-        <v>54</v>
-      </c>
-      <c r="D30" t="s">
-        <v>55</v>
-      </c>
-      <c r="E30" t="s">
-        <v>71</v>
-      </c>
-      <c r="F30" t="b">
+      <c r="H36" t="b">
         <v>1</v>
       </c>
     </row>
